--- a/frontend/public/templates/bioark-service-bulk-upload-template.xlsx
+++ b/frontend/public/templates/bioark-service-bulk-upload-template.xlsx
@@ -618,7 +618,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:N1"/>
+  <dimension ref="A1:O1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
@@ -635,6 +635,7 @@
     <col width="22" customWidth="1" min="12" max="12"/>
     <col width="22" customWidth="1" min="13" max="13"/>
     <col width="22" customWidth="1" min="14" max="14"/>
+    <col width="38" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1" ht="38" customHeight="1">
@@ -708,10 +709,15 @@
           <t>active</t>
         </is>
       </c>
+      <c r="O1" s="2" t="inlineStr">
+        <is>
+          <t>short_description</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N1001"/>
-  <conditionalFormatting sqref="A2:N1001">
+  <autoFilter ref="A1:O1001"/>
+  <conditionalFormatting sqref="A2:O1001">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
@@ -752,7 +758,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:C31"/>
+  <dimension ref="B2:C32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -1051,6 +1057,18 @@
       <c r="C31" s="11" t="inlineStr">
         <is>
           <t>Yes or No. Blank defaults to Yes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="28" customHeight="1">
+      <c r="B32" s="12" t="inlineStr">
+        <is>
+          <t>short_description</t>
+        </is>
+      </c>
+      <c r="C32" s="13" t="inlineStr">
+        <is>
+          <t>Optional one-line customer-facing summary used on catalog display cards (maximum 500 characters).</t>
         </is>
       </c>
     </row>
